--- a/output/pdf_financials_xlsx/MDMA.xlsx
+++ b/output/pdf_financials_xlsx/MDMA.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.947739</v>
+        <v>1.233912</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.536408</v>
+        <v>1.553607</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.63708</v>
+        <v>2.741193</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.49364</v>
+        <v>-0.779813</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.351033</v>
+        <v>-0.666166</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.084744</v>
+        <v>-2.188857</v>
       </c>
     </row>
     <row r="12">
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.195042</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.419379</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.040187</v>
       </c>
     </row>
     <row r="35">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.195042</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.419379</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.920473</v>
+        <v>0.96066</v>
       </c>
     </row>
     <row r="37">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.372269</v>
+        <v>0.177227</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.482532</v>
+        <v>0.063153</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.298143</v>
+        <v>0.257956</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">

--- a/output/pdf_financials_xlsx/MDMA.xlsx
+++ b/output/pdf_financials_xlsx/MDMA.xlsx
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.114547</v>
+        <v>-0.115744</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.008018000000000001</v>
+        <v>-0.010491</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.110725</v>
+        <v>0.116981</v>
       </c>
     </row>
     <row r="102">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.013143</v>
+        <v>-0.01434</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.160104</v>
+        <v>-0.162577</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.100757</v>
+        <v>0.107013</v>
       </c>
     </row>
     <row r="107">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002918</v>
       </c>
     </row>
     <row r="112">
@@ -2595,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002918</v>
       </c>
     </row>
     <row r="135">
@@ -2611,7 +2611,7 @@
         <v>-0.32136</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.043697</v>
+        <v>-1.046615</v>
       </c>
     </row>
   </sheetData>
@@ -4182,7 +4182,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>-0.001197</v>
       </c>
@@ -4391,7 +4395,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
